--- a/calendars/source/syllabus.xlsx
+++ b/calendars/source/syllabus.xlsx
@@ -8,18 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD765827-B96D-46A0-8A71-3C7B69919021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155A5EBA-39D4-4728-975E-A45EA2048F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="719" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="719" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="BuddhistHermntk (HermPrax)" sheetId="1" r:id="rId1"/>
-    <sheet name="Shurangama Sutra (Śūr)" sheetId="2" r:id="rId2"/>
-    <sheet name="Sanskrit (Skrt)" sheetId="6" r:id="rId3"/>
-    <sheet name="_Recurring" sheetId="5" r:id="rId4"/>
+    <sheet name="BuddhistHermntk (BudHerm)" sheetId="1" r:id="rId1"/>
+    <sheet name="Shurangama Sutra (楞嚴經)" sheetId="2" r:id="rId2"/>
+    <sheet name="Sanskrit (संस्कृतम्)" sheetId="6" r:id="rId3"/>
+    <sheet name="Yogācāra (Yogācāra)" sheetId="10" r:id="rId4"/>
+    <sheet name="_Recurring" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -31,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="142">
   <si>
     <t>date</t>
   </si>
@@ -42,18 +54,6 @@
     <t>title</t>
   </si>
   <si>
-    <t>detail</t>
-  </si>
-  <si>
-    <t>pages</t>
-  </si>
-  <si>
-    <t>source</t>
-  </si>
-  <si>
-    <t>link</t>
-  </si>
-  <si>
     <t>notes</t>
   </si>
   <si>
@@ -93,64 +93,10 @@
     <t>Student presentations / contemplative exercise</t>
   </si>
   <si>
-    <t>Meets 8/17, 8/19, 8/21.</t>
-  </si>
-  <si>
-    <t>Meets 8/24, 8/26, 8/28.</t>
-  </si>
-  <si>
     <t>Exam</t>
   </si>
   <si>
-    <t>Meets 8/31, 9/2, 9/4.</t>
-  </si>
-  <si>
-    <t>Meets 9/9, 9/11.</t>
-  </si>
-  <si>
-    <t>Meets 9/14, 9/16, 9/18.</t>
-  </si>
-  <si>
-    <t>Meets 9/21, 9/23, 9/25.</t>
-  </si>
-  <si>
-    <t>Contemplative Exercise Immersion 9/28-10/1.</t>
-  </si>
-  <si>
-    <t>Meets 10/5, 10/7, 10/9.</t>
-  </si>
-  <si>
-    <t>Meets 10/12, 10/14, 10/16.</t>
-  </si>
-  <si>
-    <t>Meets 10/19, 10/21, 10/23. Syllabus prints "10/29, 21, 23"; 10/29 corrected to 10/19.</t>
-  </si>
-  <si>
-    <t>Meets 10/26, 10/28, 10/30.</t>
-  </si>
-  <si>
     <t>Midterm</t>
-  </si>
-  <si>
-    <t>Meets 11/2, 11/4, 11/6.</t>
-  </si>
-  <si>
-    <t>Meets 11/9, 11/11, 11/13.</t>
-  </si>
-  <si>
-    <t>11/16-11/20.</t>
-  </si>
-  <si>
-    <t>Meets 11/23, 11/25, 11/27. Confirm 11/27 — the Friday after Thanksgiving.</t>
-  </si>
-  <si>
-    <t>Meets 11/30, 12/2, 12/4.</t>
-  </si>
-  <si>
-    <t>Meets 12/7, 12/9, 12/11.</t>
-  </si>
-  <si>
-    <t>Date TBA; anchored to the final week 12/7-12/11.</t>
   </si>
   <si>
     <t>class</t>
@@ -346,10 +292,1540 @@
     <t xml:space="preserve">Sying An [Xing 'an]. An Exhortation to Resolve Upon Bodhi. Reader pp. 1-12. Consult book for commentary. </t>
   </si>
   <si>
-    <t>Śūr</t>
-  </si>
-  <si>
-    <t>HermPrax</t>
+    <t>BudHerm</t>
+  </si>
+  <si>
+    <t>楞嚴經</t>
+  </si>
+  <si>
+    <t>(paper due by 5pm – upload to Google Classroom)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Waldron’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Making Sense of Mind Only </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>[chapter 4 to the end] </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Triṃśikā </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(Thirty Verses) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ācārya Vasubandhu’s Thirty Verses (Triṁśikā)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, tr. and explained by Mattia Salvini based  on Sthiramati’s commentary. Read the verses carefully (reader) and skim the commentary  (pp. 20-119 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>https://d3zr9vspdnjxi.cloudfront.net/sites/saugata1/sup/7739033--c-rya Vasubandhu-s-Thirty-Verses-Tri-ik-A-Manual-for-Students-2022.pdf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>) as needed. This is  an introductory framework for the whole semester. You don’t need to master everything  this week. We will unpack these verses during the rest of the semester. </t>
+    </r>
+  </si>
+  <si>
+    <t>Yogācāra’s goal </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Triṃśikā </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>verses 1-2 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Laṅkāvatārasūtra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>pages 71-83, 90-93, and 181-5 (LXIV) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Saddharmasmṛtyupasthānasūtra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapter 2, pages 509-515 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xuanzang’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Three Texts on Consciousness Only </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">chap. 1, pages 9-20, 39-43, and 298-302 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(Verses 1-2ab) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Laukikamārga </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">(mundane path) of the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Śrāvakabhūmi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>vol. 2 (=</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Yogācārabhūmi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>), pages 446- 452 </t>
+    </r>
+  </si>
+  <si>
+    <t>ālaya </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Triṃśikā </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>verses 2-5a </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Scripture on the Explication of Underlying Meaning </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Saṃdhinirmocana Sūtra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>) pages  27-29 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Asaṅga’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Summary of the Great Vehicle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mahāyānasaṃgraha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>) chapter 1 pages 13-36 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pravṛtti </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Nivṛtti Portions </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">of the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Viniścayasaṃgrahaṇī </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">of the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yogācārabhūmi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">in  Waldron’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Buddhist Unconscious </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>pages 178-89 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Pañcaskandaka </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>with Sthiramati’s commentary “The Consciousness Heap” pages 327-344  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Saṃdhinirmocana Sūtra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapter 6, pages 51-55 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ālaya </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(cont.) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Triṃśikā </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>verses 2cd-4 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xuanzang’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Three Texts on Consciousness Only </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapters 2-3 (Verses 2cd-4), pp. 47-111 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Maitreya’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Distinguishing the Middle from the Extremes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Madhyāntavibhāgabhāṣyam</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)  pages 176-77 </t>
+    </r>
+  </si>
+  <si>
+    <t>kliṣṭamanas </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Triṃśikā </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>verses 5-8a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Paramārthagāthās </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-27 and 42-44 (tr. Wayman) and 28-41 and their commentary (tr.  Schmithausen) from the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yogācārabhūmi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>pages 335-341 and 229-241, respectively </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Pañcaskandhaka </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>with Sthiramati’s commentary “The Afflicted Mind” pages 344-47 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xuanzang’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Three Texts on Consciousness Only </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapter 4, pages 113-122, 128-132, 137- 140, 142-144 (Verse 5-7) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Questions of King Milinda </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2.1.1 pages 40-45  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Saddharmasmṛtyupasthānasūtra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapter 2, pages 503-505 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>pravṛttivijñāna</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>s </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Triṃśikā </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>verses 8b-16 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xuanzang’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Three Texts on Consciousness Only </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapter 5, pages 153-161 (Verses 8-9),  164-169 (Verse 10), 172-181 (Verse 11), 185-189 (Verse 12ab), 196-205 (Verse 12cd 14ab), 210-212 (Verse 14cd), 219-229 (Verses 15-16) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Asaṅga’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mahāyānasaṃgraha </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>page 11 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>pravṛttivijñāna</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>s (cont.) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Triṃśikā </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>verses 17-20 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MN 140 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Chadhātuvibhāṅgasutta </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Saddharmasmṛtyupasthānasūtra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapter 2, pages 343-455  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Optional: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Saddharmasmṛtyupasthānasūtra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(Vol 2), Appendix 4, pages 222-301 CE: four foundations of mindfulness with dependent arising</t>
+    </r>
+  </si>
+  <si>
+    <t>three natures </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Triṃśikā </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>verses 20-28</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Maitreya and Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Madhyāntavibhāgabhāṣyam </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">chapter 1, pages 117-130 Asaṅga’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mahāyānasaṃgraha </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapters 2-3, pages 37-70 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Vasubandhu’s “The Three Natures Exposition” (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Trisvabhāvanirdeśaḥ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">) pages 244-248 Maitreya and Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Madhyāntavibhāgabhāṣyam </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>page 178-183 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🡪 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>quick in-class paper topic check in</t>
+    </r>
+  </si>
+  <si>
+    <t>three natures (cont.) </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Triṃśikā </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>verses 20-28 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Maitreya and Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Madhyāntavibhāgabhāṣyam </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapter 3, pages 143-159 </t>
+    </r>
+  </si>
+  <si>
+    <t>Brennan’s “The Three Natures and the Path to Liberation in Yogācāra-Vijñānavāda  Thought” </t>
+  </si>
+  <si>
+    <t>Waldron’s “A Yogācārin approach to Collective Illusions: Cultural Unconscious, Implicit  Bias and Racism without Races” </t>
+  </si>
+  <si>
+    <t>Bayo Akomolafe’s “Dear White People” </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">practicing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">vijñaptimātratā </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>on the bodhisattva path </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Asaṅga’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mahāyānasaṃgraha </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapter 4, pages 71-77 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Maitreya and Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Madhyāntavibhāgabhāṣyam </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapter 4, pages 161-172 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bodhisattvabhūmi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(=</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Yogācārabhūmi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">) in </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Bodhisattva Path to Unsurpassed  Enlightenment </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>pages 402-413 and 450-463 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">stages and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>pāramitā</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>s on the bodhisattva path </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Triṃśikā </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>verse 29  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Asaṅga’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mahāyānasaṃgraha </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapters 5-9, pages 79-101; optional: </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Saṃdhinirmocanasūtra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">chapter 7, pages 77-98, and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Śūraṅgama Sūtra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pages 329-43 Xuanzang’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Three Texts on Consciousness Only </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">chapter 11, pages 313-323 (verse 29) </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">The Interpretation of the Buddha Land </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>pages 193-195 </t>
+    </r>
+  </si>
+  <si>
+    <t>obstacles on the path and concepts related to liberation </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Triṃśikā </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>verses 29-30 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Maitreya and Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Madhyāntavibhāgabhāṣyam </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">chapter 2, pages 131-141 Xuanzang’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Three Texts on Consciousness Only </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">chapter 11, pages 323-40 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Saddharmasmṛtyupasthānasūtra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapter 2, pages 525-527 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Laṅkāvatārasūtra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">pages 256-61; optional: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Saṃdhinirmocanasūtra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">chapter 8, pp 99-112 Asaṅga’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Mahāyānasaṃgraha </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapter 10, pages 103-119 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xuanzang’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Three Texts on Consciousness Only </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>chapters 12-14, pages 341-367 (verses  29-30) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Interpretation of the Buddha Land </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>pages 12-13, 19-20, 24-25, 107-111 CE: the pure land as the mind of wisdom, as “pure conscious construction”</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vasubandhu’s </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Twenty Verses </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -359,7 +1835,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,6 +1859,53 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -392,10 +1915,47 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -404,7 +1964,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -425,6 +1985,42 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -646,10 +2242,10 @@
         <v>46252</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -657,10 +2253,10 @@
         <v>46259</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -668,10 +2264,10 @@
         <v>46259</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -679,10 +2275,10 @@
         <v>46266</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -690,10 +2286,10 @@
         <v>46273</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -701,10 +2297,10 @@
         <v>46280</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -712,10 +2308,10 @@
         <v>46280</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="37.5" x14ac:dyDescent="0.35">
@@ -723,10 +2319,10 @@
         <v>46280</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="50" x14ac:dyDescent="0.35">
@@ -734,10 +2330,10 @@
         <v>46287</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -745,10 +2341,10 @@
         <v>46287</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="125" x14ac:dyDescent="0.35">
@@ -756,10 +2352,10 @@
         <v>46287</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="87.5" x14ac:dyDescent="0.35">
@@ -767,10 +2363,10 @@
         <v>46301</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -778,10 +2374,10 @@
         <v>46301</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -789,10 +2385,10 @@
         <v>46308</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -800,10 +2396,10 @@
         <v>46308</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="37.5" x14ac:dyDescent="0.35">
@@ -811,10 +2407,10 @@
         <v>46315</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -822,10 +2418,10 @@
         <v>46315</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="37.5" x14ac:dyDescent="0.35">
@@ -833,10 +2429,10 @@
         <v>46322</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="37.5" x14ac:dyDescent="0.35">
@@ -844,10 +2440,10 @@
         <v>46329</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="112.5" x14ac:dyDescent="0.35">
@@ -855,10 +2451,10 @@
         <v>46336</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="75" x14ac:dyDescent="0.35">
@@ -866,10 +2462,10 @@
         <v>46350</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -877,10 +2473,10 @@
         <v>46357</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -888,10 +2484,10 @@
         <v>46357</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -899,10 +2495,10 @@
         <v>46357</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -910,10 +2506,10 @@
         <v>46364</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -954,10 +2550,10 @@
         <v>46253</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -965,10 +2561,10 @@
         <v>46260</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -976,10 +2572,10 @@
         <v>46267</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -987,10 +2583,10 @@
         <v>46274</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -998,10 +2594,10 @@
         <v>46281</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -1009,10 +2605,10 @@
         <v>46288</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -1020,10 +2616,10 @@
         <v>46302</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -1031,10 +2627,10 @@
         <v>46309</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -1042,10 +2638,10 @@
         <v>46316</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -1053,10 +2649,10 @@
         <v>46323</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -1064,10 +2660,10 @@
         <v>46330</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -1075,10 +2671,10 @@
         <v>46337</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -1086,10 +2682,10 @@
         <v>46358</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25" x14ac:dyDescent="0.35">
@@ -1097,10 +2693,10 @@
         <v>46365</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1117,19 +2713,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E6D70B2-647E-4D5B-B46C-F4C853F29653}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="46" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1139,321 +2731,150 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>46258</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>46279</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>46321</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>46363</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="37.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="4" t="s">
-        <v>39</v>
-      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1468,6 +2889,773 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789C5039-6F5E-44B8-A3D5-1443D314967F}">
+  <dimension ref="A1:C64"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="12.90625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="53.36328125" style="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="20">
+        <v>46254</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="20">
+        <v>46261</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="20">
+        <f t="shared" ref="A4:A28" si="0">A3</f>
+        <v>46261</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="20">
+        <v>46268</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="20">
+        <f t="shared" si="0"/>
+        <v>46268</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="20">
+        <f t="shared" si="0"/>
+        <v>46268</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="20">
+        <f t="shared" si="0"/>
+        <v>46268</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="20">
+        <f t="shared" si="0"/>
+        <v>46268</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="20">
+        <f t="shared" si="0"/>
+        <v>46268</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="20">
+        <v>46275</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="20">
+        <f t="shared" si="0"/>
+        <v>46275</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="20">
+        <f t="shared" si="0"/>
+        <v>46275</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="20">
+        <f t="shared" si="0"/>
+        <v>46275</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="20">
+        <f t="shared" si="0"/>
+        <v>46275</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="20">
+        <f t="shared" si="0"/>
+        <v>46275</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="20">
+        <f t="shared" si="0"/>
+        <v>46275</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="20">
+        <v>46282</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="20">
+        <f t="shared" si="0"/>
+        <v>46282</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="20">
+        <f t="shared" si="0"/>
+        <v>46282</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="20">
+        <f t="shared" si="0"/>
+        <v>46282</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="20">
+        <v>46289</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="20">
+        <f t="shared" si="0"/>
+        <v>46289</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="20">
+        <f t="shared" si="0"/>
+        <v>46289</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="20">
+        <f t="shared" si="0"/>
+        <v>46289</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="20">
+        <f t="shared" si="0"/>
+        <v>46289</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="20">
+        <f t="shared" si="0"/>
+        <v>46289</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="20">
+        <f t="shared" si="0"/>
+        <v>46289</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="20">
+        <v>46303</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="20">
+        <f t="shared" ref="A30:A32" si="1">A29</f>
+        <v>46303</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="20">
+        <f t="shared" si="1"/>
+        <v>46303</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="20">
+        <f t="shared" si="1"/>
+        <v>46303</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="20">
+        <v>46310</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="20">
+        <f t="shared" ref="A34:A37" si="2">A33</f>
+        <v>46310</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="20">
+        <f t="shared" si="2"/>
+        <v>46310</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="20">
+        <f t="shared" si="2"/>
+        <v>46310</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="20">
+        <f t="shared" si="2"/>
+        <v>46310</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="20">
+        <v>46317</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="20">
+        <f t="shared" ref="A39:A42" si="3">A38</f>
+        <v>46317</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="20">
+        <f t="shared" si="3"/>
+        <v>46317</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="20">
+        <f t="shared" si="3"/>
+        <v>46317</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="20">
+        <f t="shared" si="3"/>
+        <v>46317</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="20">
+        <v>46324</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="20">
+        <f t="shared" ref="A44:A48" si="4">A43</f>
+        <v>46324</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="20">
+        <f t="shared" si="4"/>
+        <v>46324</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="20">
+        <f t="shared" si="4"/>
+        <v>46324</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="20">
+        <f t="shared" si="4"/>
+        <v>46324</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="20">
+        <f t="shared" si="4"/>
+        <v>46324</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="20">
+        <v>46331</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="20">
+        <f t="shared" ref="A50:A52" si="5">A49</f>
+        <v>46331</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="20">
+        <f t="shared" si="5"/>
+        <v>46331</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="20">
+        <f t="shared" si="5"/>
+        <v>46331</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="20">
+        <v>46338</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="20">
+        <f t="shared" ref="A54:A57" si="6">A53</f>
+        <v>46338</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="20">
+        <f t="shared" si="6"/>
+        <v>46338</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="20">
+        <f t="shared" si="6"/>
+        <v>46338</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="20">
+        <f t="shared" si="6"/>
+        <v>46338</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="20">
+        <v>46359</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="20">
+        <f t="shared" ref="A59:A63" si="7">A58</f>
+        <v>46359</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="20">
+        <f t="shared" si="7"/>
+        <v>46359</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="20">
+        <f t="shared" si="7"/>
+        <v>46359</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="20">
+        <f t="shared" si="7"/>
+        <v>46359</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="20">
+        <f t="shared" si="7"/>
+        <v>46359</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="20">
+        <v>46366</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1486,7 +3674,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -1495,45 +3683,45 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F2" s="2">
         <v>46257</v>
@@ -1545,26 +3733,26 @@
         <v>1</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F3" s="2">
         <v>46258</v>
@@ -1576,7 +3764,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -1584,65 +3772,65 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/calendars/source/syllabus.xlsx
+++ b/calendars/source/syllabus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69698B53-E87F-4413-90EC-11769F94A8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A58DDA-CD5C-49C1-B1D5-089561845421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="149">
   <si>
     <t>date</t>
   </si>
@@ -2003,6 +2003,9 @@
   </si>
   <si>
     <t>Saturday</t>
+  </si>
+  <si>
+    <t>Friday</t>
   </si>
 </sst>
 </file>
@@ -12169,13 +12172,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E8" s="25">
-        <v>0.79166666666666663</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="F8" s="21">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="G8" s="21">
         <v>46340</v>
